--- a/材料库编码索引（自用）0608.xlsx
+++ b/材料库编码索引（自用）0608.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="276">
   <si>
     <t>宇辰物料编码</t>
   </si>
@@ -41,16 +41,19 @@
     <t>大类代码</t>
   </si>
   <si>
-    <t>工厂类型</t>
-  </si>
-  <si>
-    <t>二级/三级代码</t>
-  </si>
-  <si>
-    <t>二级/三级分类</t>
-  </si>
-  <si>
-    <t>单位</t>
+    <t>一级分类</t>
+  </si>
+  <si>
+    <t>二级代码</t>
+  </si>
+  <si>
+    <t>二级分类</t>
+  </si>
+  <si>
+    <t>三级代码</t>
+  </si>
+  <si>
+    <t>三级分类</t>
   </si>
   <si>
     <t>成本价</t>
@@ -132,6 +135,9 @@
   </si>
   <si>
     <t>S007</t>
+  </si>
+  <si>
+    <t>柜体、家具五金</t>
   </si>
   <si>
     <t>JL</t>
@@ -1528,7 +1534,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1537,6 +1543,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1558,6 +1567,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2113,8 +2125,8 @@
     <col min="5" max="5" width="27.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.1272727272727" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.4545454545455" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1818181818182" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.0909090909091" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1818181818182" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5454545454545" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2131,7 +2143,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2140,42 +2152,44 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="4" t="str">
         <f>B2&amp;"-"&amp;D2&amp;"-"&amp;F2&amp;"-"&amp;TEXT(0+ROW(A1),"000")</f>
         <v>S001-SM-SP-001</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="E2" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2184,25 +2198,25 @@
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="4" t="str">
         <f t="shared" ref="A3:A34" si="0">B3&amp;"-"&amp;D3&amp;"-"&amp;F3&amp;"-"&amp;TEXT(0+ROW(A2),"000")</f>
         <v>S002-SM-KJ-002</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -2211,25 +2225,25 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="3" t="str">
+      <c r="A4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S003-SM-HY-003</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9"/>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2238,23 +2252,23 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="3" t="str">
+      <c r="A5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S004-SM-SJ-004</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>25</v>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2263,23 +2277,23 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="3" t="str">
+      <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S005-SM-PT-005</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
+      <c r="B6" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9"/>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -2288,23 +2302,23 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="3" t="str">
+      <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S006-SM-QT-006</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>31</v>
+      <c r="B7" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="8"/>
+      <c r="D7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="9"/>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2313,175 +2327,177 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A8" s="4" t="str">
+        <f>B8&amp;"-"&amp;D8&amp;"-"&amp;H8&amp;"-"&amp;TEXT(0+ROW(A7),"000")</f>
         <v>S007-SM-JL-007</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>34</v>
+      <c r="B8" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="D8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A9" s="4" t="str">
+        <f>B9&amp;"-"&amp;D9&amp;"-"&amp;H9&amp;"-"&amp;TEXT(0+ROW(A8),"000")</f>
         <v>S008-SM-GD-008</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>37</v>
+      <c r="B9" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="D9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A10" s="4" t="str">
+        <f>B10&amp;"-"&amp;D10&amp;"-"&amp;H10&amp;"-"&amp;TEXT(0+ROW(A9),"000")</f>
         <v>S009-SM-LS-009</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>40</v>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A11" s="4" t="str">
+        <f>B11&amp;"-"&amp;D11&amp;"-"&amp;H11&amp;"-"&amp;TEXT(0+ROW(A10),"000")</f>
         <v>S010-SM-CT-010</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>43</v>
+      <c r="B11" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A12" s="4" t="str">
+        <f>B12&amp;"-"&amp;D12&amp;"-"&amp;H12&amp;"-"&amp;TEXT(0+ROW(A11),"000")</f>
         <v>S011-SM-PJ-011</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>46</v>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="D12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="A13" s="4" t="str">
+        <f>B13&amp;"-"&amp;D13&amp;"-"&amp;H13&amp;"-"&amp;TEXT(0+ROW(A12),"000")</f>
         <v>S012-SM-LH-012</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>49</v>
+      <c r="B13" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="D13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="3" t="str">
+      <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S013-MD-SM-013</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>52</v>
+      <c r="B14" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>54</v>
+      <c r="D14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2490,23 +2506,23 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="3" t="str">
+      <c r="A15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S014-MD-SF-014</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>56</v>
+      <c r="B15" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="11"/>
+      <c r="D15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="13"/>
       <c r="F15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2515,23 +2531,23 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="3" t="str">
+      <c r="A16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S015-MD-QH-015</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>59</v>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="11"/>
+      <c r="D16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="13"/>
       <c r="F16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2540,23 +2556,23 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="3" t="str">
+      <c r="A17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S016-MD-SP-016</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>62</v>
+      <c r="B17" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="11"/>
+      <c r="D17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="13"/>
       <c r="F17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2565,23 +2581,23 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="3" t="str">
+      <c r="A18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S017-MD-LT-017</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>64</v>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="11"/>
+      <c r="D18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="13"/>
       <c r="F18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -2590,23 +2606,23 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="3" t="str">
+      <c r="A19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S018-MD-WP-018</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>67</v>
+      <c r="B19" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="11"/>
+      <c r="D19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="13"/>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2615,23 +2631,23 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="3" t="str">
+      <c r="A20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S019-MD-QT-019</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>70</v>
+      <c r="B20" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="12"/>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="14"/>
       <c r="F20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2640,25 +2656,25 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="3" t="str">
+      <c r="A21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S020-DT-BL-020</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>72</v>
+      <c r="B21" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>74</v>
+      <c r="D21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2667,23 +2683,23 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="3" t="str">
+      <c r="A22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S021-DT-QL-021</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>77</v>
+      <c r="B22" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="11"/>
+      <c r="D22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="13"/>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2692,23 +2708,23 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="3" t="str">
+      <c r="A23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S022-DT-DL-022</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>80</v>
+      <c r="B23" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="11"/>
+      <c r="D23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="13"/>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2717,23 +2733,23 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="3" t="str">
+      <c r="A24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S023-DT-YM-023</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>83</v>
+      <c r="B24" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="11"/>
+      <c r="D24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="13"/>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2742,23 +2758,23 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="3" t="str">
+      <c r="A25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S024-DT-ZQ-024</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>86</v>
+      <c r="B25" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="11"/>
+      <c r="D25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="13"/>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2767,25 +2783,25 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="3" t="str">
+      <c r="A26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S025-CZ-LM-025</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>89</v>
+      <c r="B26" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>91</v>
+      <c r="D26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2794,23 +2810,23 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="3" t="str">
+      <c r="A27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S026-CZ-YG-026</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>94</v>
+      <c r="B27" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="11"/>
+      <c r="D27" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="13"/>
       <c r="F27" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2819,23 +2835,23 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="3" t="str">
+      <c r="A28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S027-CZ-JL-027</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>97</v>
+      <c r="B28" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="11"/>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="13"/>
       <c r="F28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2844,23 +2860,23 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="3" t="str">
+      <c r="A29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S028-CZ-MK-028</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>99</v>
+      <c r="B29" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="11"/>
+      <c r="D29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="13"/>
       <c r="F29" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2869,23 +2885,23 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="3" t="str">
+      <c r="A30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S029-CZ-YB-029</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>102</v>
+      <c r="B30" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="12"/>
+      <c r="D30" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="14"/>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2894,25 +2910,25 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="3" t="str">
+      <c r="A31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S030-SC-DL-030</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>105</v>
+      <c r="B31" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>107</v>
+      <c r="D31" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2921,23 +2937,23 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="3" t="str">
+      <c r="A32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S031-SC-HY-031</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>109</v>
+      <c r="B32" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="11"/>
+      <c r="D32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="13"/>
       <c r="F32" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2946,23 +2962,23 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="3" t="str">
+      <c r="A33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S032-SC-SY-032</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>111</v>
+      <c r="B33" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="11"/>
+      <c r="D33" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="13"/>
       <c r="F33" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2971,23 +2987,23 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="3" t="str">
+      <c r="A34" s="4" t="str">
         <f t="shared" si="0"/>
         <v>S033-SC-BY-033</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>114</v>
+      <c r="B34" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="11"/>
+      <c r="D34" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="13"/>
       <c r="F34" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2996,23 +3012,23 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="3" t="str">
+      <c r="A35" s="4" t="str">
         <f t="shared" ref="A35:A66" si="1">B35&amp;"-"&amp;D35&amp;"-"&amp;F35&amp;"-"&amp;TEXT(0+ROW(A34),"000")</f>
         <v>S034-SC-SH-034</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>117</v>
+      <c r="B35" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="11"/>
+      <c r="D35" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="13"/>
       <c r="F35" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -3021,23 +3037,23 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="3" t="str">
+      <c r="A36" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S035-SC-SZ-035</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>120</v>
+      <c r="B36" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="11"/>
+      <c r="D36" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="13"/>
       <c r="F36" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -3046,23 +3062,23 @@
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="3" t="str">
+      <c r="A37" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S036-SC-WZ-036</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>123</v>
+      <c r="B37" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="11"/>
+      <c r="D37" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="13"/>
       <c r="F37" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -3071,23 +3087,23 @@
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="3" t="str">
+      <c r="A38" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S037-SC-GS-037</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>126</v>
+      <c r="B38" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" s="11"/>
+      <c r="D38" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="13"/>
       <c r="F38" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -3096,23 +3112,23 @@
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="3" t="str">
+      <c r="A39" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S038-SC-WJ-038</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>129</v>
+      <c r="B39" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="12"/>
+      <c r="D39" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="14"/>
       <c r="F39" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -3121,25 +3137,25 @@
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="3" t="str">
+      <c r="A40" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S039-WY-LT-039</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>132</v>
+      <c r="B40" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>134</v>
+      <c r="D40" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -3148,23 +3164,23 @@
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="3" t="str">
+      <c r="A41" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S040-WY-FT-040</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>136</v>
+      <c r="B41" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" s="11"/>
+      <c r="D41" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="13"/>
       <c r="F41" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -3173,23 +3189,23 @@
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="3" t="str">
+      <c r="A42" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S041-WY-BT-041</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>139</v>
+      <c r="B42" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E42" s="11"/>
+      <c r="D42" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="13"/>
       <c r="F42" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -3198,23 +3214,23 @@
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="3" t="str">
+      <c r="A43" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S042-WY-ZN-042</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>142</v>
+      <c r="B43" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" s="11"/>
+      <c r="D43" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="13"/>
       <c r="F43" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -3223,23 +3239,23 @@
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="3" t="str">
+      <c r="A44" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S043-WY-ZG-043</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>145</v>
+      <c r="B44" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" s="11"/>
+      <c r="D44" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="13"/>
       <c r="F44" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -3248,23 +3264,23 @@
       <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="3" t="str">
+      <c r="A45" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S044-WY-TS-044</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>148</v>
+      <c r="B45" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E45" s="11"/>
+      <c r="D45" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" s="13"/>
       <c r="F45" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -3273,23 +3289,23 @@
       <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="3" t="str">
+      <c r="A46" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S045-WY-TZ-045</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>151</v>
+      <c r="B46" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" s="11"/>
+      <c r="D46" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="13"/>
       <c r="F46" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -3298,23 +3314,23 @@
       <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="3" t="str">
+      <c r="A47" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S046-WY-TX-046</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>154</v>
+      <c r="B47" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" s="11"/>
+      <c r="D47" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="13"/>
       <c r="F47" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -3323,23 +3339,23 @@
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="3" t="str">
+      <c r="A48" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S047-WY-YT-047</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>157</v>
+      <c r="B48" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="11"/>
+      <c r="D48" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="13"/>
       <c r="F48" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -3348,23 +3364,23 @@
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="3" t="str">
+      <c r="A49" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S048-WY-GP-048</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>160</v>
+      <c r="B49" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="11"/>
+      <c r="D49" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="13"/>
       <c r="F49" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -3373,23 +3389,23 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="3" t="str">
+      <c r="A50" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S049-WY-DC-049</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>163</v>
+      <c r="B50" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" s="11"/>
+      <c r="D50" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E50" s="13"/>
       <c r="F50" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -3398,23 +3414,23 @@
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="3" t="str">
+      <c r="A51" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S050-WY-SC-050</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>166</v>
+      <c r="B51" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" s="11"/>
+      <c r="D51" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="13"/>
       <c r="F51" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -3423,23 +3439,23 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="3" t="str">
+      <c r="A52" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S051-WY-YX-051</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>168</v>
+      <c r="B52" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="C52" s="2"/>
-      <c r="D52" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E52" s="11"/>
+      <c r="D52" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E52" s="13"/>
       <c r="F52" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -3448,23 +3464,23 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="3" t="str">
+      <c r="A53" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S052-WY-YS-052</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>171</v>
+      <c r="B53" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="C53" s="2"/>
-      <c r="D53" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E53" s="11"/>
+      <c r="D53" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E53" s="13"/>
       <c r="F53" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -3473,23 +3489,23 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="3" t="str">
+      <c r="A54" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S053-WY-TB-053</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>174</v>
+      <c r="B54" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="C54" s="2"/>
-      <c r="D54" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E54" s="11"/>
+      <c r="D54" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" s="13"/>
       <c r="F54" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -3498,23 +3514,23 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="3" t="str">
+      <c r="A55" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S054-WY-BB-054</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>177</v>
+      <c r="B55" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="C55" s="2"/>
-      <c r="D55" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E55" s="11"/>
+      <c r="D55" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E55" s="13"/>
       <c r="F55" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -3523,23 +3539,23 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="3" t="str">
+      <c r="A56" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S055-WY-YG-055</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>180</v>
+      <c r="B56" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="C56" s="2"/>
-      <c r="D56" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E56" s="11"/>
+      <c r="D56" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="13"/>
       <c r="F56" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -3548,23 +3564,23 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="3" t="str">
+      <c r="A57" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S056-WY-AM-056</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>182</v>
+      <c r="B57" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="C57" s="2"/>
-      <c r="D57" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="12"/>
+      <c r="D57" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="14"/>
       <c r="F57" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -3573,25 +3589,25 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="3" t="str">
+      <c r="A58" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S057-YW-MP-057</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>185</v>
+      <c r="B58" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="C58" s="2"/>
-      <c r="D58" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>187</v>
+      <c r="D58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -3600,23 +3616,23 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="3" t="str">
+      <c r="A59" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S058-YW-CF-058</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>190</v>
+      <c r="B59" s="5" t="s">
+        <v>192</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E59" s="11"/>
+      <c r="D59" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" s="13"/>
       <c r="F59" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -3625,23 +3641,23 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="3" t="str">
+      <c r="A60" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S059-YW-LY-059</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>193</v>
+      <c r="B60" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E60" s="11"/>
+      <c r="D60" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" s="13"/>
       <c r="F60" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -3650,23 +3666,23 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="3" t="str">
+      <c r="A61" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S060-YW-QT-060</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>196</v>
+      <c r="B61" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E61" s="11"/>
+      <c r="D61" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E61" s="13"/>
       <c r="F61" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -3675,23 +3691,23 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="3" t="str">
+      <c r="A62" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S061-YW-MZ-061</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>198</v>
+      <c r="B62" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E62" s="11"/>
+      <c r="D62" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" s="13"/>
       <c r="F62" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -3700,23 +3716,23 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="3" t="str">
+      <c r="A63" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S062-YW-ZW-062</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>201</v>
+      <c r="B63" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="11"/>
+      <c r="D63" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63" s="13"/>
       <c r="F63" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -3725,23 +3741,23 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="3" t="str">
+      <c r="A64" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S063-YW-PF-063</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>204</v>
+      <c r="B64" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E64" s="11"/>
+      <c r="D64" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="13"/>
       <c r="F64" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -3750,23 +3766,23 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="3" t="str">
+      <c r="A65" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S064-YW-DS-064</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>207</v>
+      <c r="B65" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E65" s="11"/>
+      <c r="D65" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="13"/>
       <c r="F65" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -3775,23 +3791,23 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="3" t="str">
+      <c r="A66" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S065-YW-YJ-065</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>210</v>
+      <c r="B66" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E66" s="11"/>
+      <c r="D66" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E66" s="13"/>
       <c r="F66" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -3800,23 +3816,23 @@
       <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="3" t="str">
+      <c r="A67" s="4" t="str">
         <f t="shared" ref="A67:A87" si="2">B67&amp;"-"&amp;D67&amp;"-"&amp;F67&amp;"-"&amp;TEXT(0+ROW(A66),"000")</f>
         <v>S066-YW-DZ-066</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>213</v>
+      <c r="B67" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="11"/>
+      <c r="D67" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E67" s="13"/>
       <c r="F67" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -3825,23 +3841,23 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12">
-      <c r="A68" s="3" t="str">
+      <c r="A68" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S067-YW-DL-067</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>216</v>
+      <c r="B68" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="12"/>
+      <c r="D68" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" s="14"/>
       <c r="F68" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -3850,25 +3866,25 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="3" t="str">
+      <c r="A69" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S068-HM-MM-068</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>218</v>
+      <c r="B69" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>220</v>
+      <c r="D69" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>222</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3877,23 +3893,23 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12">
-      <c r="A70" s="3" t="str">
+      <c r="A70" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S069-HM-LH-069</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>223</v>
+      <c r="B70" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="C70" s="2"/>
-      <c r="D70" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E70" s="11"/>
+      <c r="D70" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E70" s="13"/>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -3902,23 +3918,23 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="3" t="str">
+      <c r="A71" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S070-HM-SM-070</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>225</v>
+      <c r="B71" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C71" s="2"/>
-      <c r="D71" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E71" s="11"/>
+      <c r="D71" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E71" s="13"/>
       <c r="F71" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -3927,23 +3943,23 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="3" t="str">
+      <c r="A72" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S071-HM-HY-071</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>227</v>
+      <c r="B72" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E72" s="11"/>
+      <c r="D72" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E72" s="13"/>
       <c r="F72" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -3952,23 +3968,23 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="3" t="str">
+      <c r="A73" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S072-HM-LS-072</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>229</v>
+      <c r="B73" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E73" s="11"/>
+      <c r="D73" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E73" s="13"/>
       <c r="F73" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -3977,23 +3993,23 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="3" t="str">
+      <c r="A74" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S073-HM-MP-073</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>230</v>
+      <c r="B74" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E74" s="12"/>
+      <c r="D74" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E74" s="14"/>
       <c r="F74" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -4002,25 +4018,25 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12">
-      <c r="A75" s="3" t="str">
+      <c r="A75" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S074-DJ-QR-074</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>232</v>
+      <c r="B75" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C75" s="2"/>
-      <c r="D75" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>234</v>
+      <c r="D75" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -4029,23 +4045,23 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12">
-      <c r="A76" s="3" t="str">
+      <c r="A76" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S075-DJ-DD-075</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>237</v>
+      <c r="B76" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="C76" s="2"/>
-      <c r="D76" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E76" s="11"/>
+      <c r="D76" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E76" s="13"/>
       <c r="F76" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -4054,23 +4070,23 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12">
-      <c r="A77" s="3" t="str">
+      <c r="A77" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S076-DJ-BD-076</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>240</v>
+      <c r="B77" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E77" s="11"/>
+      <c r="D77" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E77" s="13"/>
       <c r="F77" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -4079,23 +4095,23 @@
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="3" t="str">
+      <c r="A78" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S077-DJ-KG-077</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>243</v>
+      <c r="B78" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="C78" s="2"/>
-      <c r="D78" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E78" s="11"/>
+      <c r="D78" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E78" s="13"/>
       <c r="F78" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -4104,23 +4120,23 @@
       <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12">
-      <c r="A79" s="3" t="str">
+      <c r="A79" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S078-DJ-PQ-078</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>246</v>
+      <c r="B79" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="C79" s="2"/>
-      <c r="D79" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E79" s="12"/>
+      <c r="D79" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E79" s="14"/>
       <c r="F79" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -4129,25 +4145,25 @@
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12">
-      <c r="A80" s="3" t="str">
+      <c r="A80" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S079-DQ-YY-079</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>249</v>
+      <c r="B80" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="C80" s="2"/>
-      <c r="D80" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>251</v>
+      <c r="D80" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -4156,23 +4172,23 @@
       <c r="L80" s="2"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="3" t="str">
+      <c r="A81" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S080-DQ-RZ-080</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>254</v>
+      <c r="B81" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="C81" s="2"/>
-      <c r="D81" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81" s="11"/>
+      <c r="D81" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E81" s="13"/>
       <c r="F81" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -4181,23 +4197,23 @@
       <c r="L81" s="2"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="3" t="str">
+      <c r="A82" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S081-DQ-DC-081</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>257</v>
+      <c r="B82" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="C82" s="2"/>
-      <c r="D82" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E82" s="11"/>
+      <c r="D82" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E82" s="13"/>
       <c r="F82" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -4206,23 +4222,23 @@
       <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="3" t="str">
+      <c r="A83" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S082-DQ-XW-082</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>259</v>
+      <c r="B83" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="C83" s="2"/>
-      <c r="D83" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E83" s="11"/>
+      <c r="D83" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E83" s="13"/>
       <c r="F83" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -4231,23 +4247,23 @@
       <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="3" t="str">
+      <c r="A84" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S083-DQ-WB-083</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>262</v>
+      <c r="B84" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="C84" s="2"/>
-      <c r="D84" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E84" s="11"/>
+      <c r="D84" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E84" s="13"/>
       <c r="F84" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -4256,23 +4272,23 @@
       <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="3" t="str">
+      <c r="A85" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S084-DQ-ZK-084</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>265</v>
+      <c r="B85" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E85" s="11"/>
+      <c r="D85" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E85" s="13"/>
       <c r="F85" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -4281,23 +4297,23 @@
       <c r="L85" s="2"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="3" t="str">
+      <c r="A86" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S085-DQ-RS-085</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>268</v>
+      <c r="B86" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="C86" s="2"/>
-      <c r="D86" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E86" s="11"/>
+      <c r="D86" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E86" s="13"/>
       <c r="F86" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -4306,23 +4322,23 @@
       <c r="L86" s="2"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="3" t="str">
+      <c r="A87" s="4" t="str">
         <f t="shared" si="2"/>
         <v>S086-DQ-KT-086</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>271</v>
+      <c r="B87" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="C87" s="2"/>
-      <c r="D87" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E87" s="12"/>
+      <c r="D87" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E87" s="14"/>
       <c r="F87" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -4331,7 +4347,7 @@
       <c r="L87" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="E2:E13"/>
     <mergeCell ref="E14:E20"/>
     <mergeCell ref="E21:E25"/>
@@ -4342,6 +4358,7 @@
     <mergeCell ref="E69:E74"/>
     <mergeCell ref="E75:E79"/>
     <mergeCell ref="E80:E87"/>
+    <mergeCell ref="F8:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="8" scale="80" orientation="portrait"/>
